--- a/Información_reportes_Mensuales.xlsx
+++ b/Información_reportes_Mensuales.xlsx
@@ -6086,7 +6086,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7572,7 +7572,7 @@
     <row r="91" spans="1:8">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuente: Min. Energia, Reporte de Proyectos agosto 2026 (/MIN ENERGIA/), Tablas 4 y 6, + busqueda abierta al 2026-10-01.</t>
+          <t xml:space="preserve">Fuente: Min. Energia, Reporte de Proyectos agosto 2026 (/MIN ENERGIA/), Tablas 4 y 6, + busqueda abierta al 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">En construccion (sept-26)</t>
+          <t xml:space="preserve">En construccion (sept-26); operacion comercial prevista 2027</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTA</t>
+          <t xml:space="preserve">Se mantiene (alta 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTA</t>
+          <t xml:space="preserve">Se mantiene (alta 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTA</t>
+          <t xml:space="preserve">Se mantiene (alta 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -7942,290 +7942,532 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Se mantiene (alta 2026-10-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERNC Antofagasta (ampliacion BESS)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grupo Ibereolica Renovables</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>990</v>
+      </c>
+      <c r="D105">
+        <v>4950</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ampliacion de almacenamiento en consulta de pertinencia ante el SEA (resultado no publicado); proyecto base con RCA, 1.218 MW</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:8">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Black BESS</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baja ya ejecutada en la corrida 2026-09-24: BESS - Gabriela Solar (Grenergy, 220 MW / 1.100 MWh) entro en operacion.</t>
+          <t xml:space="preserve">Inversiones Black Solar (Grupo Mack Energy)</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>350</v>
+      </c>
+      <c r="D106">
+        <v>1409</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RCA aprobada abr-2026; Camarones, Arica y Parinacota; US$220 M; construccion 16 meses, inicio no confirmado</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:8">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sidon Solar (BESS)</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umbral aplicado: &gt;= ~1000 MWh. Quedan fuera por poco BESS Monte Aguila (Grenergy, 240 MW / 960 MWh) y</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="B108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BESS Copiapo Solar (Atlas, 233 MW / 932 MWh).</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">Sidon Solar SpA (Trina Solar)</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>150</v>
+      </c>
+      <c r="D107">
+        <v>1296</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RCA aprobada 07-oct-2026 (DIA); Cabrero (Biobio) / Pemuco (Nuble); US$100 M; 158,17 MWdc FV asociados</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" spans="1:8"/>
     <row r="109" spans="1:8">
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">A vigilar (aprobados ambientalmente en ago-26, aun sin construccion): BESS Imilac (FPG, 360 MW / 1.800 MWh) y</t>
+          <t xml:space="preserve">Bajas en esta corrida: ninguna. Se verifico Pampas y Cristales (AES Andes): siguen con operacion comercial prevista</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIA BESS (GAIA Chile, 200 MW / 1.163 MWh) - Min. Energia ago-26, Tabla 12.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="B112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fuentes de las 4 altas de esta corrida: ess-news.com 01-09-2026 (Guanchoi); ess-news.com 31-08-2026 (Antofagasta 1);</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">para 2027, no entraron en operacion. Baja ya ejecutada en la corrida 2026-09-24: BESS - Gabriela Solar (Grenergy,</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220 MW / 1.100 MWh) entro en operacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:8"/>
     <row r="113" spans="1:8">
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">reporteminero.cl / portalminero.com 09-2026 (Las Bateas, ingreso SEIA 15-09-2026); ess-news.com 13-08-2026 (Huanil).</t>
+          <t xml:space="preserve">Umbral aplicado: &gt;= ~1000 MWh. Quedan fuera por poco BESS Monte Aguila (Grenergy, 240 MW / 960 MWh) y</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">PFV Antofagasta 1 repite el dimensionamiento de Elena Fase I (430 MW / 3.010 MWh) pero es otro ingreso al SEIA, en</t>
+          <t xml:space="preserve">BESS Copiapo Solar (Atlas, 233 MW / 932 MWh).</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maria Elena (Antofagasta) y con otro calendario; se listan por separado, no es la misma fila duplicada.</t>
+          <t xml:space="preserve">A vigilar (aprobados ambientalmente en ago-26, aun sin construccion): BESS Imilac (FPG, 360 MW / 1.800 MWh) y</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">De BESS Las Bateas la fuente publica solo los MWh; su potencia en MW no esta publicada y no se estima (queda 'n/d').</t>
+          <t xml:space="preserve">GAIA BESS (GAIA Chile, 200 MW / 1.163 MWh) - Min. Energia ago-26, Tabla 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quedan fuera por no tener MWh publicado: BESS Ganso (Limes, 150 MW / 5 h, Valparaiso) y Las Salinas BESS (Enel,</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BITACORA DE CORRIDAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corrida</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Universo base instalada</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura MW (Alta)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura MW (Alta+Media)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Novedades de atribucion</t>
-        </is>
-      </c>
-    </row>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205 MW / 4 h, en construccion). Las fuentes publican solo MW y horas; el MWh no se estima (regla de CLAUDE.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" spans="1:8"/>
     <row r="120" spans="1:8">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-27</t>
-        </is>
-      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACERA jul-26: 2.655 MW / 11.250 MWh</t>
-        </is>
-      </c>
-      <c r="C120">
-        <v>0.118</v>
-      </c>
-      <c r="D120">
-        <v>0.17</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Construccion inicial de la hoja: 4 proyectos atribuidos, 19 excluidos.</t>
+          <t xml:space="preserve">Fuentes de las 4 altas de la corrida 2026-10-01: ess-news.com 01-09-2026 (Guanchoi); ess-news.com 31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-10</t>
-        </is>
-      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACERA jul-26: 2.655 MW / 11.250 MWh (sin cambio)</t>
-        </is>
-      </c>
-      <c r="C121">
-        <v>0.118</v>
-      </c>
-      <c r="D121">
-        <v>0.17</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se repitio la busqueda amplia: NINGUNA atribucion nueva confirmada.</t>
+          <t xml:space="preserve">(Antofagasta 1); reporteminero.cl / portalminero.com 09-2026 (Las Bateas); ess-news.com 13-08-2026 (Huanil).</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-10 (2a)</t>
-        </is>
-      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACERA jul-26: 2.655 MW / 11.250 MWh (sin cambio)</t>
-        </is>
-      </c>
-      <c r="C122">
-        <v>0.118</v>
-      </c>
-      <c r="D122">
-        <v>0.17</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sin atribucion nueva. Se incorpora la lista de Main future projects.</t>
+          <t xml:space="preserve">Fuentes de las 3 altas de esta corrida (2026-10-08): saurenergy.com + ess-news.com 13-01-2026 (ERNC Antofagasta);</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-24</t>
-        </is>
-      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACERA ago-26: 3.116 MW / 13.522 MWh</t>
-        </is>
-      </c>
-      <c r="C123">
-        <v>0.1</v>
-      </c>
-      <c r="D123">
-        <v>0.145</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NUEVA atribucion Alta: BESS Elena Fase I = BYD (MC Cube-T). No entra al share: esta En Pruebas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-01</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACERA ago-26: 3.116 MW / 13.522 MWh (ACERA no publico sep-26 al cierre)</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Market share fuera de alcance (CLAUDE.md 29-09-2026). No se recalcula cobertura. Solo se actualiza la seccion 7.</t>
+          <t xml:space="preserve">ess-news.com 15-04-2026 + pv-magazine-latam.com 09-04-2026 (Black BESS); ess-news.com 08-10-2026 (Sidon Solar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="1:8"/>
+    <row r="125" spans="1:8">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PFV Antofagasta 1 repite el dimensionamiento de Elena Fase I (430 MW / 3.010 MWh) pero es otro ingreso al SEIA, en</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nota corrida 2026-09-24</t>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maria Elena (Antofagasta) y con otro calendario; se listan por separado, no es la misma fila duplicada.</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se verifico proyecto por proyecto la Tabla 2 (5 sistemas que entraron en operacion en agosto, 498 MW / 2.452 MWh):</t>
+          <t xml:space="preserve">De BESS Las Bateas la fuente publica solo los MWh; su potencia en MW no esta publicada y no se estima (queda 'n/d').</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ninguno de los 5 tiene fabricante publicado. Engie no divulga proveedor en Libelula / Los Loros / Arica II; para</t>
+          <t xml:space="preserve">ERNC Antofagasta (Ibereolica) NO es el mismo proyecto que PFV Antofagasta 1 (Grenergy): distinto titular, distinto</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabriela (Grenergy) la prensa cita 'BYD y CATL' como proveedores de fases del complejo Oasis de Atacama sin</t>
+          <t xml:space="preserve">tamano (990 MW / 4.950 MWh vs 430 MW / 3.010 MWh) y distinto expediente. Ambos en la Region de Antofagasta.</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">atribuir cual corresponde a esta fase, por lo que NO se le asigna fabricante (regla 2).</t>
+          <t xml:space="preserve">SENALIZADO (ERNC Antofagasta): la cifra 990 MW / 4.950 MWh viene de una sola fuente de prensa especializada y la</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consulta de pertinencia ante el SEA no tiene resultado publicado. El proyecto base (1.218 MW) si tiene RCA, pero con</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nota corrida 2026-10-01</t>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solo 15 MW de BESS. Se carga por tamano, con la etapa explicita; si el SEA rechaza la ampliacion, corresponde la baja.</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">El market share por fabricante salio del alcance de la Routine (CLAUDE.md, 29-09-2026). Las secciones 1 a 6 de esta</t>
+          <t xml:space="preserve">SENALIZADO (Sidon Solar): la fuente declara 1.296 MWh y a la vez "150 MW por cinco horas" (= 750 MWh), cifras que no</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="B134" t="inlineStr">
         <is>
+          <t xml:space="preserve">cuadran entre si y que la fuente no reconcilia. Se carga el MWh publicado (1.296); la discrepancia queda a la vista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" spans="1:8"/>
+    <row r="136" spans="1:8">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BITACORA DE CORRIDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrida</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Universo base instalada</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura MW (Alta)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura MW (Alta+Media)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Novedades de atribucion</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACERA jul-26: 2.655 MW / 11.250 MWh</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>0.118</v>
+      </c>
+      <c r="D138">
+        <v>0.17</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construccion inicial de la hoja: 4 proyectos atribuidos, 19 excluidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACERA jul-26: 2.655 MW / 11.250 MWh (sin cambio)</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>0.118</v>
+      </c>
+      <c r="D139">
+        <v>0.17</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se repitio la busqueda amplia: NINGUNA atribucion nueva confirmada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-10 (2a)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACERA jul-26: 2.655 MW / 11.250 MWh (sin cambio)</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>0.118</v>
+      </c>
+      <c r="D140">
+        <v>0.17</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin atribucion nueva. Se incorpora la lista de Main future projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-24</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACERA ago-26: 3.116 MW / 13.522 MWh</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>0.1</v>
+      </c>
+      <c r="D141">
+        <v>0.145</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUEVA atribucion Alta: BESS Elena Fase I = BYD (MC Cube-T). No entra al share: esta En Pruebas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-01</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACERA ago-26: 3.116 MW / 13.522 MWh (ACERA no publico sep-26 al cierre)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Market share fuera de alcance (CLAUDE.md 29-09-2026). No se recalcula cobertura. Solo se actualiza la seccion 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-08</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACERA ago-26: 3.116 MW / 13.522 MWh (ACERA sigue sin publicar sep-26)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Market share fuera de alcance. Ninguna de las 5 fuentes publico dato nuevo; solo se actualiza la seccion 7 (3 altas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" spans="1:8"/>
+    <row r="145" spans="1:8">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota corrida 2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se verifico proyecto por proyecto la Tabla 2 (5 sistemas que entraron en operacion en agosto, 498 MW / 2.452 MWh):</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ninguno de los 5 tiene fabricante publicado. Engie no divulga proveedor en Libelula / Los Loros / Arica II; para</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabriela (Grenergy) la prensa cita 'BYD y CATL' como proveedores de fases del complejo Oasis de Atacama sin</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atribuir cual corresponde a esta fase, por lo que NO se le asigna fabricante (regla 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" spans="1:8"/>
+    <row r="151" spans="1:8">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota corrida 2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El market share por fabricante salio del alcance de la Routine (CLAUDE.md, 29-09-2026). Las secciones 1 a 6 de esta</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="B153" t="inlineStr">
+        <is>
           <t xml:space="preserve">hoja quedan congeladas como registro historico de la ultima corrida que si lo calculo (2026-09-24): no se actualizan</t>
         </is>
       </c>
     </row>
-    <row r="135" spans="1:8">
-      <c r="B135" t="inlineStr">
+    <row r="154" spans="1:8">
+      <c r="B154" t="inlineStr">
         <is>
           <t xml:space="preserve">ni se borran. Lo unico que la Routine sigue manteniendo aca es la seccion 7, Main Future Projects, que CLAUDE.md si</t>
         </is>
       </c>
     </row>
-    <row r="136" spans="1:8">
-      <c r="B136" t="inlineStr">
+    <row r="155" spans="1:8">
+      <c r="B155" t="inlineStr">
         <is>
           <t xml:space="preserve">mantiene en alcance. Si vuelve a incorporarse el market share, se reactivan desde esa linea de base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" spans="1:8"/>
+    <row r="157" spans="1:8">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota corrida 2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrida sin dato nuevo de fuente: ACERA no publico el boletin de sep-26 (verificado: la URL predecible del CDN</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">responde 403 AccessDenied mientras la de ago-26 responde 200, y el centro de informacion sigue mostrando ago-26),</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la CNE no publico RMensual_v202610 (404), y no hay PDFs nuevos en /COORDINADOR/, /MIN ENERGIA/ ni /GENERADORAS/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por eso las filas 2-15 de la hoja BESS y la tabla de Energy Matrix quedan sin cambio: no hay nada que cargar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El trabajo de esta corrida es la seccion 7 (3 altas) mas la copia fechada en /historial/.</t>
         </is>
       </c>
     </row>

--- a/Información_reportes_Mensuales.xlsx
+++ b/Información_reportes_Mensuales.xlsx
@@ -10,6 +10,7 @@
     <sheet name="BESS" sheetId="1" r:id="rId1"/>
     <sheet name="Energy Matrix" sheetId="2" r:id="rId2"/>
     <sheet name="Market Share Estimate" sheetId="3" r:id="rId7"/>
+    <sheet name="ACERA Summary" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
@@ -95,7 +96,7 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Evolución capacidad BESS según fecha estimada de interconexión (Updated August 2026 — E. Abierta, datos al 31-jul-2026)</t>
+    <t>Evolución capacidad BESS según fecha estimada de interconexión (Updated September 2026 — E. Abierta, datos al 31-ago-2026)</t>
   </si>
   <si>
     <t>Acumulado</t>
@@ -966,7 +967,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>242</c:v>
+                  <c:v>702</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>25</c:v>
@@ -1011,7 +1012,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>840</c:v>
+                  <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -1269,61 +1270,61 @@
                   <c:v>16784</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17026</c:v>
+                  <c:v>17486</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17051</c:v>
+                  <c:v>17511</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17111</c:v>
+                  <c:v>17571</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17111</c:v>
+                  <c:v>17571</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18717</c:v>
+                  <c:v>19177</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>19697</c:v>
+                  <c:v>20157</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19733</c:v>
+                  <c:v>20193</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>19769</c:v>
+                  <c:v>20229</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>19808</c:v>
+                  <c:v>20268</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1771,7 +1772,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>(JUNE 2026)</a:t>
+              <a:t>(JULY 2026)</a:t>
             </a:r>
             <a:endParaRPr lang="es-MX"/>
           </a:p>
@@ -4224,7 +4225,9 @@
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>3293</v>
+      </c>
       <c r="D9" s="1">
         <v>2291</v>
       </c>
@@ -4235,14 +4238,18 @@
         <v>6</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>15272</v>
+      </c>
       <c r="J9" s="1">
         <v>10057</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="1"/>
+      <c r="M9" s="1">
+        <v>1709</v>
+      </c>
       <c r="N9" s="1">
         <v>2760</v>
       </c>
@@ -4256,7 +4263,9 @@
       <c r="R9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="S9" s="1"/>
+      <c r="S9" s="1">
+        <v>7297</v>
+      </c>
       <c r="T9" s="1">
         <v>13593</v>
       </c>
@@ -4266,7 +4275,9 @@
       <c r="X9" s="14">
         <v>5219</v>
       </c>
-      <c r="Y9" s="1"/>
+      <c r="Y9" s="1">
+        <v>5555</v>
+      </c>
       <c r="Z9" s="1">
         <f>+(4705+505)</f>
         <v>5210</v>
@@ -4277,7 +4288,9 @@
       <c r="AC9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="1"/>
+      <c r="AD9" s="1">
+        <v>24061</v>
+      </c>
       <c r="AE9" s="1">
         <v>21175</v>
       </c>
@@ -4286,7 +4299,9 @@
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>3293</v>
+      </c>
       <c r="D10" s="1">
         <v>2625</v>
       </c>
@@ -4297,14 +4312,18 @@
         <v>7</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>15272</v>
+      </c>
       <c r="J10" s="1">
         <v>11250</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1">
+        <v>1709</v>
+      </c>
       <c r="N10" s="1">
         <v>3183</v>
       </c>
@@ -4318,7 +4337,9 @@
       <c r="R10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S10" s="1"/>
+      <c r="S10" s="1">
+        <v>7297</v>
+      </c>
       <c r="T10" s="1">
         <v>14698</v>
       </c>
@@ -4328,7 +4349,9 @@
       <c r="X10" s="1">
         <v>4972</v>
       </c>
-      <c r="Y10" s="1"/>
+      <c r="Y10" s="1">
+        <v>5590</v>
+      </c>
       <c r="Z10" s="1">
         <f>+(4268+705)</f>
         <v>4973.0</v>
@@ -4339,7 +4362,9 @@
       <c r="AC10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AD10" s="1"/>
+      <c r="AD10" s="1">
+        <v>24223</v>
+      </c>
       <c r="AE10" s="1">
         <v>21721</v>
       </c>
@@ -4348,7 +4373,9 @@
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1">
+        <v>3510</v>
+      </c>
       <c r="D11" s="1">
         <v>3123</v>
       </c>
@@ -4359,14 +4386,18 @@
         <v>8</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>16002</v>
+      </c>
       <c r="J11" s="1">
         <v>13522</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1">
+        <v>2113</v>
+      </c>
       <c r="N11" s="1">
         <v>2686</v>
       </c>
@@ -4377,23 +4408,34 @@
       <c r="R11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S11" s="1"/>
+      <c r="S11" s="1">
+        <v>9176</v>
+      </c>
       <c r="T11" s="1">
         <v>12408</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
+      <c r="X11" s="1">
+        <v>5149</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>5134</v>
+      </c>
+      <c r="Z11" s="1">
+        <f>+(4368+705)</f>
+        <v>5073</v>
+      </c>
       <c r="AA11" s="1">
         <v>5217</v>
       </c>
       <c r="AC11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AD11" s="1"/>
+      <c r="AD11" s="1">
+        <v>22004</v>
+      </c>
       <c r="AE11" s="1">
         <v>22330</v>
       </c>
@@ -4868,7 +4910,7 @@
         <v>16784</v>
       </c>
       <c r="D38" s="1">
-        <v>242</v>
+        <v>702</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -4880,7 +4922,7 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" si="1"/>
-        <v>17026</v>
+        <v>17486</v>
       </c>
       <c r="D39" s="1">
         <v>25</v>
@@ -4895,7 +4937,7 @@
       </c>
       <c r="C40" s="1">
         <f t="shared" si="1"/>
-        <v>17051</v>
+        <v>17511</v>
       </c>
       <c r="D40" s="1">
         <v>60</v>
@@ -4910,7 +4952,7 @@
       </c>
       <c r="C41" s="1">
         <f t="shared" si="1"/>
-        <v>17111</v>
+        <v>17571</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -4925,7 +4967,7 @@
       </c>
       <c r="C42" s="1">
         <f t="shared" si="1"/>
-        <v>17111</v>
+        <v>17571</v>
       </c>
       <c r="D42" s="1">
         <v>1606</v>
@@ -4940,7 +4982,7 @@
       </c>
       <c r="C43" s="1">
         <f t="shared" si="1"/>
-        <v>18717</v>
+        <v>19177</v>
       </c>
       <c r="D43" s="1">
         <v>980</v>
@@ -4955,7 +4997,7 @@
       </c>
       <c r="C44" s="1">
         <f t="shared" si="1"/>
-        <v>19697</v>
+        <v>20157</v>
       </c>
       <c r="D44" s="1">
         <v>36</v>
@@ -4970,7 +5012,7 @@
       </c>
       <c r="C45" s="1">
         <f t="shared" si="1"/>
-        <v>19733</v>
+        <v>20193</v>
       </c>
       <c r="D45" s="1">
         <v>36</v>
@@ -4985,7 +5027,7 @@
       </c>
       <c r="C46" s="1">
         <f t="shared" si="1"/>
-        <v>19769</v>
+        <v>20229</v>
       </c>
       <c r="D46" s="1">
         <v>15</v>
@@ -5000,7 +5042,7 @@
       </c>
       <c r="C47" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -5015,7 +5057,7 @@
       </c>
       <c r="C48" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -5030,7 +5072,7 @@
       </c>
       <c r="C49" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D49" s="1">
         <v>24</v>
@@ -5045,7 +5087,7 @@
       </c>
       <c r="C50" s="1">
         <f t="shared" si="1"/>
-        <v>19808</v>
+        <v>20268</v>
       </c>
       <c r="D50" s="1">
         <v>616</v>
@@ -5060,7 +5102,7 @@
       </c>
       <c r="C51" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -5075,7 +5117,7 @@
       </c>
       <c r="C52" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -5090,10 +5132,10 @@
       </c>
       <c r="C53" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D53" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -5105,7 +5147,7 @@
       </c>
       <c r="C54" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -5120,7 +5162,7 @@
       </c>
       <c r="C55" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -5135,7 +5177,7 @@
       </c>
       <c r="C56" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -5150,7 +5192,7 @@
       </c>
       <c r="C57" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D57" s="1">
         <v>162</v>
@@ -5665,7 +5707,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-24 (Routine mensual) - ver bitacora al final</t>
+          <t xml:space="preserve">2026-09-24 fue la ultima corrida de market share. Desde la corrida 2026-10 el market share quedo fuera de alcance (CLAUDE.md): las secciones 1-6 se congelan como registro historico y solo se mantiene al dia la seccion 7 (Main Future Projects).</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7165,7 @@
     <row r="91" spans="1:8">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuente: Ministerio de Energia, Reporte de Proyectos agosto 2026 (/MIN ENERGIA/), Tablas 4 y 6.</t>
+          <t xml:space="preserve">Fuente: Ministerio de Energia, Reporte de Proyectos agosto 2026 (/MIN ENERGIA/), Tablas 4 y 6 - no hubo reporte nuevo disponible al 15-10-2026 - mas investigacion abierta de la corrida 2026-10.</t>
         </is>
       </c>
     </row>
@@ -7386,35 +7428,37 @@
     <row r="101" spans="1:8">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BESS - Gabriela Solar</t>
+          <t xml:space="preserve">BESS Las Bateas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grenergy</t>
-        </is>
-      </c>
-      <c r="C101">
-        <v>220</v>
+          <t xml:space="preserve">BESS Las Bateas SpA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/d</t>
+        </is>
       </c>
       <c r="D101">
-        <v>1100</v>
+        <v>1765</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">En operacion desde ago-2026</t>
+          <t xml:space="preserve">En evaluacion ambiental (ingreso al SEIA, sept-2026)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJA: entro en operacion (Min. Energia ago-26, Tabla 2)</t>
+          <t xml:space="preserve">ALTA: proyecto nuevo &gt;= ~1.000 MWh identificado en investigacion abierta</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabricante de estos proyectos: solo BESS Elena Fase I tiene atribucion publica confirmada (BYD). Los otros 7 no.</t>
+          <t xml:space="preserve">Fabricante de estos proyectos: solo BESS Elena Fase I tiene atribucion publica confirmada (BYD). Los otros 8 no. (Nota historica: la atribucion de fabricante ya no se investiga, ver B2.)</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7486,14 @@
     <row r="107" spans="1:8">
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIA BESS (GAIA Chile, 200 MW / 1.163 MWh) - Min. Energia ago-26, Tabla 12.</t>
+          <t xml:space="preserve">GAIA BESS (GAIA Chile, 200 MW / 1.163 MWh) - Min. Energia ago-26, Tabla 12. Sin cambios verificables esta corrida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrida 2026-10: BESS Lile (Engie, 142 MW / 802 MWh) entro en operacion comercial el 25-09-2026 (autorizacion CEN). Queda bajo el umbral de ~1.000 MWh, por lo que no entra ni sale de esta tabla; se anota porque figura 'En pruebas' en la seccion 6, congelada a ago-26.</t>
         </is>
       </c>
     </row>
@@ -7610,4 +7661,474 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS Situation in Chile (ACERA, 2026)</t>
+        </is>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operation</t>
+        </is>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construction</t>
+        </is>
+      </c>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Month</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MWh</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MWh</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enero</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>IF(BESS!E4="","",BESS!E4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f>IF(BESS!J4="","",BESS!J4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>IF(BESS!P4="","",BESS!P4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>IF(BESS!T4="","",BESS!T4)</f>
+        <v/>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f>IF(BESS!AA4="","",BESS!AA4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f>IF(BESS!AE4="","",BESS!AE4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Febrero</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>IF(BESS!E5="","",BESS!E5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f>IF(BESS!J5="","",BESS!J5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>IF(BESS!P5="","",BESS!P5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>IF(BESS!T5="","",BESS!T5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f>IF(BESS!AA5="","",BESS!AA5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f>IF(BESS!AE5="","",BESS!AE5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marzo</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>IF(BESS!E6="","",BESS!E6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f>IF(BESS!J6="","",BESS!J6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>IF(BESS!P6="","",BESS!P6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>IF(BESS!T6="","",BESS!T6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f>IF(BESS!AA6="","",BESS!AA6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f>IF(BESS!AE6="","",BESS!AE6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abril</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>IF(BESS!E7="","",BESS!E7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>IF(BESS!J7="","",BESS!J7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>IF(BESS!P7="","",BESS!P7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>IF(BESS!T7="","",BESS!T7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>IF(BESS!AA7="","",BESS!AA7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>IF(BESS!AE7="","",BESS!AE7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mayo</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>IF(BESS!E8="","",BESS!E8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f>IF(BESS!J8="","",BESS!J8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>IF(BESS!P8="","",BESS!P8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>IF(BESS!T8="","",BESS!T8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f>IF(BESS!AA8="","",BESS!AA8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f>IF(BESS!AE8="","",BESS!AE8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junio</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>IF(BESS!E9="","",BESS!E9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>IF(BESS!J9="","",BESS!J9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>IF(BESS!P9="","",BESS!P9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>IF(BESS!T9="","",BESS!T9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>IF(BESS!AA9="","",BESS!AA9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f>IF(BESS!AE9="","",BESS!AE9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julio</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>IF(BESS!E10="","",BESS!E10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>IF(BESS!J10="","",BESS!J10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>IF(BESS!P10="","",BESS!P10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f>IF(BESS!T10="","",BESS!T10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>IF(BESS!AA10="","",BESS!AA10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>IF(BESS!AE10="","",BESS!AE10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agosto</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>IF(BESS!E11="","",BESS!E11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>IF(BESS!J11="","",BESS!J11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>IF(BESS!P11="","",BESS!P11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>IF(BESS!T11="","",BESS!T11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>IF(BESS!AA11="","",BESS!AA11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f>IF(BESS!AE11="","",BESS!AE11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Septiembre</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="str">
+        <f>IF(BESS!E12="","",BESS!E12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f>IF(BESS!J12="","",BESS!J12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="1" t="str">
+        <f>IF(BESS!P12="","",BESS!P12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f>IF(BESS!T12="","",BESS!T12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f>IF(BESS!AA12="","",BESS!AA12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f>IF(BESS!AE12="","",BESS!AE12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Octubre</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="str">
+        <f>IF(BESS!E13="","",BESS!E13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f>IF(BESS!J13="","",BESS!J13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="1" t="str">
+        <f>IF(BESS!P13="","",BESS!P13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f>IF(BESS!T13="","",BESS!T13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="1" t="str">
+        <f>IF(BESS!AA13="","",BESS!AA13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f>IF(BESS!AE13="","",BESS!AE13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Noviembre</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="str">
+        <f>IF(BESS!E14="","",BESS!E14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f>IF(BESS!J14="","",BESS!J14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="1" t="str">
+        <f>IF(BESS!P14="","",BESS!P14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f>IF(BESS!T14="","",BESS!T14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="1" t="str">
+        <f>IF(BESS!AA14="","",BESS!AA14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f>IF(BESS!AE14="","",BESS!AE14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diciembre</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="str">
+        <f>IF(BESS!E15="","",BESS!E15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f>IF(BESS!J15="","",BESS!J15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="1" t="str">
+        <f>IF(BESS!P15="","",BESS!P15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f>IF(BESS!T15="","",BESS!T15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="1" t="str">
+        <f>IF(BESS!AA15="","",BESS!AA15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f>IF(BESS!AE15="","",BESS!AE15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tabla de fórmulas: toma las columnas de fuente ACERA de la hoja BESS (E/J/P/T/AA/AE). Celda vacía = ACERA aún no publicó ese mes. No editar a mano.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Información_reportes_Mensuales.xlsx
+++ b/Información_reportes_Mensuales.xlsx
@@ -95,7 +95,7 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Evolución capacidad BESS según fecha estimada de interconexión (Updated August 2026 — E. Abierta, datos al 31-jul-2026)</t>
+    <t>Evolución capacidad BESS según fecha estimada de interconexión (Updated October 2026 — E. Abierta, datos al 31-ago-2026)</t>
   </si>
   <si>
     <t>Acumulado</t>
@@ -966,7 +966,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>242</c:v>
+                  <c:v>702</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>25</c:v>
@@ -1011,7 +1011,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>840</c:v>
+                  <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -1269,61 +1269,61 @@
                   <c:v>16784</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17026</c:v>
+                  <c:v>17486</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17051</c:v>
+                  <c:v>17511</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17111</c:v>
+                  <c:v>17571</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17111</c:v>
+                  <c:v>17571</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18717</c:v>
+                  <c:v>19177</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>19697</c:v>
+                  <c:v>20157</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19733</c:v>
+                  <c:v>20193</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>19769</c:v>
+                  <c:v>20229</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>19808</c:v>
+                  <c:v>20268</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3734,7 +3734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AE57"/>
+  <dimension ref="A2:AE74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
@@ -4384,7 +4384,9 @@
       <c r="W11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="X11" s="1"/>
+      <c r="X11" s="1">
+        <v>5149</v>
+      </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1">
@@ -4404,37 +4406,49 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1">
+        <v>3125</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1">
+        <v>13555</v>
+      </c>
       <c r="L12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
+      <c r="P12" s="1">
+        <v>3017</v>
+      </c>
       <c r="R12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
+      <c r="T12" s="1">
+        <v>13735</v>
+      </c>
       <c r="W12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
+      <c r="AA12" s="1">
+        <v>5130</v>
+      </c>
       <c r="AC12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
+      <c r="AE12" s="1">
+        <v>22123</v>
+      </c>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -4868,7 +4882,7 @@
         <v>16784</v>
       </c>
       <c r="D38" s="1">
-        <v>242</v>
+        <v>702</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -4880,7 +4894,7 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" si="1"/>
-        <v>17026</v>
+        <v>17486</v>
       </c>
       <c r="D39" s="1">
         <v>25</v>
@@ -4895,7 +4909,7 @@
       </c>
       <c r="C40" s="1">
         <f t="shared" si="1"/>
-        <v>17051</v>
+        <v>17511</v>
       </c>
       <c r="D40" s="1">
         <v>60</v>
@@ -4910,7 +4924,7 @@
       </c>
       <c r="C41" s="1">
         <f t="shared" si="1"/>
-        <v>17111</v>
+        <v>17571</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -4925,7 +4939,7 @@
       </c>
       <c r="C42" s="1">
         <f t="shared" si="1"/>
-        <v>17111</v>
+        <v>17571</v>
       </c>
       <c r="D42" s="1">
         <v>1606</v>
@@ -4940,7 +4954,7 @@
       </c>
       <c r="C43" s="1">
         <f t="shared" si="1"/>
-        <v>18717</v>
+        <v>19177</v>
       </c>
       <c r="D43" s="1">
         <v>980</v>
@@ -4955,7 +4969,7 @@
       </c>
       <c r="C44" s="1">
         <f t="shared" si="1"/>
-        <v>19697</v>
+        <v>20157</v>
       </c>
       <c r="D44" s="1">
         <v>36</v>
@@ -4970,7 +4984,7 @@
       </c>
       <c r="C45" s="1">
         <f t="shared" si="1"/>
-        <v>19733</v>
+        <v>20193</v>
       </c>
       <c r="D45" s="1">
         <v>36</v>
@@ -4985,7 +4999,7 @@
       </c>
       <c r="C46" s="1">
         <f t="shared" si="1"/>
-        <v>19769</v>
+        <v>20229</v>
       </c>
       <c r="D46" s="1">
         <v>15</v>
@@ -5000,7 +5014,7 @@
       </c>
       <c r="C47" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -5015,7 +5029,7 @@
       </c>
       <c r="C48" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -5030,7 +5044,7 @@
       </c>
       <c r="C49" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D49" s="1">
         <v>24</v>
@@ -5045,7 +5059,7 @@
       </c>
       <c r="C50" s="1">
         <f t="shared" si="1"/>
-        <v>19808</v>
+        <v>20268</v>
       </c>
       <c r="D50" s="1">
         <v>616</v>
@@ -5060,7 +5074,7 @@
       </c>
       <c r="C51" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -5075,7 +5089,7 @@
       </c>
       <c r="C52" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -5090,10 +5104,10 @@
       </c>
       <c r="C53" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D53" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -5105,7 +5119,7 @@
       </c>
       <c r="C54" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -5120,7 +5134,7 @@
       </c>
       <c r="C55" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -5135,7 +5149,7 @@
       </c>
       <c r="C56" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -5150,20 +5164,385 @@
       </c>
       <c r="C57" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D57" s="1">
         <v>162</v>
       </c>
     </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS Situation in Chile (ACERA, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operation</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Month</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MWh</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MWh</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">January</t>
+        </is>
+      </c>
+      <c r="B63" s="1">
+        <f>IF(BESS!E4="","",BESS!E4)</f>
+      </c>
+      <c r="C63" s="1">
+        <f>IF(BESS!J4="","",BESS!J4)</f>
+      </c>
+      <c r="D63" s="1">
+        <f>IF(BESS!P4="","",BESS!P4)</f>
+      </c>
+      <c r="E63" s="1">
+        <f>IF(BESS!T4="","",BESS!T4)</f>
+      </c>
+      <c r="F63" s="1">
+        <f>IF(BESS!AA4="","",BESS!AA4)</f>
+      </c>
+      <c r="G63" s="1">
+        <f>IF(BESS!AE4="","",BESS!AE4)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">February</t>
+        </is>
+      </c>
+      <c r="B64" s="1">
+        <f>IF(BESS!E5="","",BESS!E5)</f>
+      </c>
+      <c r="C64" s="1">
+        <f>IF(BESS!J5="","",BESS!J5)</f>
+      </c>
+      <c r="D64" s="1">
+        <f>IF(BESS!P5="","",BESS!P5)</f>
+      </c>
+      <c r="E64" s="1">
+        <f>IF(BESS!T5="","",BESS!T5)</f>
+      </c>
+      <c r="F64" s="1">
+        <f>IF(BESS!AA5="","",BESS!AA5)</f>
+      </c>
+      <c r="G64" s="1">
+        <f>IF(BESS!AE5="","",BESS!AE5)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">March</t>
+        </is>
+      </c>
+      <c r="B65" s="1">
+        <f>IF(BESS!E6="","",BESS!E6)</f>
+      </c>
+      <c r="C65" s="1">
+        <f>IF(BESS!J6="","",BESS!J6)</f>
+      </c>
+      <c r="D65" s="1">
+        <f>IF(BESS!P6="","",BESS!P6)</f>
+      </c>
+      <c r="E65" s="1">
+        <f>IF(BESS!T6="","",BESS!T6)</f>
+      </c>
+      <c r="F65" s="1">
+        <f>IF(BESS!AA6="","",BESS!AA6)</f>
+      </c>
+      <c r="G65" s="1">
+        <f>IF(BESS!AE6="","",BESS!AE6)</f>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">April</t>
+        </is>
+      </c>
+      <c r="B66" s="1">
+        <f>IF(BESS!E7="","",BESS!E7)</f>
+      </c>
+      <c r="C66" s="1">
+        <f>IF(BESS!J7="","",BESS!J7)</f>
+      </c>
+      <c r="D66" s="1">
+        <f>IF(BESS!P7="","",BESS!P7)</f>
+      </c>
+      <c r="E66" s="1">
+        <f>IF(BESS!T7="","",BESS!T7)</f>
+      </c>
+      <c r="F66" s="1">
+        <f>IF(BESS!AA7="","",BESS!AA7)</f>
+      </c>
+      <c r="G66" s="1">
+        <f>IF(BESS!AE7="","",BESS!AE7)</f>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">May</t>
+        </is>
+      </c>
+      <c r="B67" s="1">
+        <f>IF(BESS!E8="","",BESS!E8)</f>
+      </c>
+      <c r="C67" s="1">
+        <f>IF(BESS!J8="","",BESS!J8)</f>
+      </c>
+      <c r="D67" s="1">
+        <f>IF(BESS!P8="","",BESS!P8)</f>
+      </c>
+      <c r="E67" s="1">
+        <f>IF(BESS!T8="","",BESS!T8)</f>
+      </c>
+      <c r="F67" s="1">
+        <f>IF(BESS!AA8="","",BESS!AA8)</f>
+      </c>
+      <c r="G67" s="1">
+        <f>IF(BESS!AE8="","",BESS!AE8)</f>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">June</t>
+        </is>
+      </c>
+      <c r="B68" s="1">
+        <f>IF(BESS!E9="","",BESS!E9)</f>
+      </c>
+      <c r="C68" s="1">
+        <f>IF(BESS!J9="","",BESS!J9)</f>
+      </c>
+      <c r="D68" s="1">
+        <f>IF(BESS!P9="","",BESS!P9)</f>
+      </c>
+      <c r="E68" s="1">
+        <f>IF(BESS!T9="","",BESS!T9)</f>
+      </c>
+      <c r="F68" s="1">
+        <f>IF(BESS!AA9="","",BESS!AA9)</f>
+      </c>
+      <c r="G68" s="1">
+        <f>IF(BESS!AE9="","",BESS!AE9)</f>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">July</t>
+        </is>
+      </c>
+      <c r="B69" s="1">
+        <f>IF(BESS!E10="","",BESS!E10)</f>
+      </c>
+      <c r="C69" s="1">
+        <f>IF(BESS!J10="","",BESS!J10)</f>
+      </c>
+      <c r="D69" s="1">
+        <f>IF(BESS!P10="","",BESS!P10)</f>
+      </c>
+      <c r="E69" s="1">
+        <f>IF(BESS!T10="","",BESS!T10)</f>
+      </c>
+      <c r="F69" s="1">
+        <f>IF(BESS!AA10="","",BESS!AA10)</f>
+      </c>
+      <c r="G69" s="1">
+        <f>IF(BESS!AE10="","",BESS!AE10)</f>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">August</t>
+        </is>
+      </c>
+      <c r="B70" s="1">
+        <f>IF(BESS!E11="","",BESS!E11)</f>
+      </c>
+      <c r="C70" s="1">
+        <f>IF(BESS!J11="","",BESS!J11)</f>
+      </c>
+      <c r="D70" s="1">
+        <f>IF(BESS!P11="","",BESS!P11)</f>
+      </c>
+      <c r="E70" s="1">
+        <f>IF(BESS!T11="","",BESS!T11)</f>
+      </c>
+      <c r="F70" s="1">
+        <f>IF(BESS!AA11="","",BESS!AA11)</f>
+      </c>
+      <c r="G70" s="1">
+        <f>IF(BESS!AE11="","",BESS!AE11)</f>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">September</t>
+        </is>
+      </c>
+      <c r="B71" s="1">
+        <f>IF(BESS!E12="","",BESS!E12)</f>
+      </c>
+      <c r="C71" s="1">
+        <f>IF(BESS!J12="","",BESS!J12)</f>
+      </c>
+      <c r="D71" s="1">
+        <f>IF(BESS!P12="","",BESS!P12)</f>
+      </c>
+      <c r="E71" s="1">
+        <f>IF(BESS!T12="","",BESS!T12)</f>
+      </c>
+      <c r="F71" s="1">
+        <f>IF(BESS!AA12="","",BESS!AA12)</f>
+      </c>
+      <c r="G71" s="1">
+        <f>IF(BESS!AE12="","",BESS!AE12)</f>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October</t>
+        </is>
+      </c>
+      <c r="B72" s="1">
+        <f>IF(BESS!E13="","",BESS!E13)</f>
+      </c>
+      <c r="C72" s="1">
+        <f>IF(BESS!J13="","",BESS!J13)</f>
+      </c>
+      <c r="D72" s="1">
+        <f>IF(BESS!P13="","",BESS!P13)</f>
+      </c>
+      <c r="E72" s="1">
+        <f>IF(BESS!T13="","",BESS!T13)</f>
+      </c>
+      <c r="F72" s="1">
+        <f>IF(BESS!AA13="","",BESS!AA13)</f>
+      </c>
+      <c r="G72" s="1">
+        <f>IF(BESS!AE13="","",BESS!AE13)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">November</t>
+        </is>
+      </c>
+      <c r="B73" s="1">
+        <f>IF(BESS!E14="","",BESS!E14)</f>
+      </c>
+      <c r="C73" s="1">
+        <f>IF(BESS!J14="","",BESS!J14)</f>
+      </c>
+      <c r="D73" s="1">
+        <f>IF(BESS!P14="","",BESS!P14)</f>
+      </c>
+      <c r="E73" s="1">
+        <f>IF(BESS!T14="","",BESS!T14)</f>
+      </c>
+      <c r="F73" s="1">
+        <f>IF(BESS!AA14="","",BESS!AA14)</f>
+      </c>
+      <c r="G73" s="1">
+        <f>IF(BESS!AE14="","",BESS!AE14)</f>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">December</t>
+        </is>
+      </c>
+      <c r="B74" s="1">
+        <f>IF(BESS!E15="","",BESS!E15)</f>
+      </c>
+      <c r="C74" s="1">
+        <f>IF(BESS!J15="","",BESS!J15)</f>
+      </c>
+      <c r="D74" s="1">
+        <f>IF(BESS!P15="","",BESS!P15)</f>
+      </c>
+      <c r="E74" s="1">
+        <f>IF(BESS!T15="","",BESS!T15)</f>
+      </c>
+      <c r="F74" s="1">
+        <f>IF(BESS!AA15="","",BESS!AA15)</f>
+      </c>
+      <c r="G74" s="1">
+        <f>IF(BESS!AE15="","",BESS!AE15)</f>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="10">
     <mergeCell ref="AC2:AE2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="L2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7123,7 +7502,7 @@
     <row r="91" spans="1:8">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuente: Ministerio de Energia, Reporte de Proyectos agosto 2026 (/MIN ENERGIA/), Tablas 4 y 6.</t>
+          <t xml:space="preserve">Fuente: Ministerio de Energia, Reporte de Proyectos agosto 2026 (/MIN ENERGIA/), Tablas 4 y 6; ACERA Boletin Septiembre-26; investigacion abierta (corrida 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -7386,49 +7765,49 @@
     <row r="101" spans="1:8">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BESS - Gabriela Solar</t>
+          <t xml:space="preserve">BESS Huanil</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grenergy</t>
+          <t xml:space="preserve">Limes Renewable Energy</t>
         </is>
       </c>
       <c r="C101">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D101">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">En operacion desde ago-2026</t>
+          <t xml:space="preserve">Ready-to-Build (ago-26), Coquimbo; sin construccion iniciada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJA: entro en operacion (Min. Energia ago-26, Tabla 2)</t>
+          <t xml:space="preserve">ALTA: identificado en investigacion abierta; no figura en Min. Energia ago-26</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabricante de estos proyectos: solo BESS Elena Fase I tiene atribucion publica confirmada (BYD). Los otros 7 no.</t>
+          <t xml:space="preserve">Fabricante de estos proyectos: solo BESS Elena Fase I tiene atribucion publica confirmada (BYD). Los otros 8 no.</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umbral aplicado: &gt;= ~1000 MWh. Quedan fuera por poco BESS Monte Aguila (Grenergy, 240 MW / 960 MWh) y</t>
+          <t xml:space="preserve">Umbral aplicado: &gt;= ~1000 MWh. Quedan fuera por poco BESS Monte Aguila (Grenergy, 240 MW / 960 MWh),</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">BESS Copiapo Solar (Atlas, 233 MW / 932 MWh).</t>
+          <t xml:space="preserve">BESS Copiapo Solar (Atlas, 233 MW / 932 MWh) y BESS El Romero (Acciona, 196 MW / 980 MWh).</t>
         </is>
       </c>
     </row>
@@ -7446,6 +7825,13 @@
         </is>
       </c>
     </row>
+    <row r="108" spans="1:8">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baja aplicada en esta corrida: BESS - Gabriela Solar (Grenergy, 220 MW / 1.100 MWh) sale de la lista; entro en operacion en ago-2026.</t>
+        </is>
+      </c>
+    </row>
     <row r="109" spans="1:8">
       <c r="A109" t="inlineStr">
         <is>
@@ -7569,6 +7955,23 @@
       <c r="E114" t="inlineStr">
         <is>
           <t xml:space="preserve">NUEVA atribucion Alta: BESS Elena Fase I = BYD (MC Cube-T). No entra al share: esta En Pruebas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACERA sep-26: 3.125 MW / 13.555 MWh</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Market share esta fuera de alcance (CLAUDE.md): NO se rehizo la busqueda de atribucion ni se recalculo la cobertura. Solo se actualizo Main Future Projects (alta: BESS Huanil).</t>
         </is>
       </c>
     </row>

--- a/Información_reportes_Mensuales.xlsx
+++ b/Información_reportes_Mensuales.xlsx
@@ -10,6 +10,7 @@
     <sheet name="BESS" sheetId="1" r:id="rId1"/>
     <sheet name="Energy Matrix" sheetId="2" r:id="rId2"/>
     <sheet name="Market Share Estimate" sheetId="3" r:id="rId7"/>
+    <sheet name="ACERA Summary" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
@@ -95,7 +96,7 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Evolución capacidad BESS según fecha estimada de interconexión (Updated August 2026 — E. Abierta, datos al 31-jul-2026)</t>
+    <t>Evolución capacidad BESS según fecha estimada de interconexión (Updated September 2026 — E. Abierta, datos al 31-ago-2026)</t>
   </si>
   <si>
     <t>Acumulado</t>
@@ -966,7 +967,7 @@
                   <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>242</c:v>
+                  <c:v>702</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>25</c:v>
@@ -1011,7 +1012,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>840</c:v>
+                  <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -1269,61 +1270,61 @@
                   <c:v>16784</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17026</c:v>
+                  <c:v>17486</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17051</c:v>
+                  <c:v>17511</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17111</c:v>
+                  <c:v>17571</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17111</c:v>
+                  <c:v>17571</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18717</c:v>
+                  <c:v>19177</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>19697</c:v>
+                  <c:v>20157</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19733</c:v>
+                  <c:v>20193</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>19769</c:v>
+                  <c:v>20229</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>19784</c:v>
+                  <c:v>20244</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>19808</c:v>
+                  <c:v>20268</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>20424</c:v>
+                  <c:v>20884</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>21264</c:v>
+                  <c:v>21844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4384,7 +4385,9 @@
       <c r="W11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="X11" s="1"/>
+      <c r="X11" s="1">
+        <v>5149</v>
+      </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1">
@@ -4404,37 +4407,49 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1">
+        <v>3125</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1">
+        <v>13555</v>
+      </c>
       <c r="L12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
+      <c r="P12" s="1">
+        <v>3017</v>
+      </c>
       <c r="R12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
+      <c r="T12" s="1">
+        <v>13735</v>
+      </c>
       <c r="W12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
+      <c r="AA12" s="1">
+        <v>5130</v>
+      </c>
       <c r="AC12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
+      <c r="AE12" s="1">
+        <v>22123</v>
+      </c>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -4868,7 +4883,7 @@
         <v>16784</v>
       </c>
       <c r="D38" s="1">
-        <v>242</v>
+        <v>702</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -4880,7 +4895,7 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" si="1"/>
-        <v>17026</v>
+        <v>17486</v>
       </c>
       <c r="D39" s="1">
         <v>25</v>
@@ -4895,7 +4910,7 @@
       </c>
       <c r="C40" s="1">
         <f t="shared" si="1"/>
-        <v>17051</v>
+        <v>17511</v>
       </c>
       <c r="D40" s="1">
         <v>60</v>
@@ -4910,7 +4925,7 @@
       </c>
       <c r="C41" s="1">
         <f t="shared" si="1"/>
-        <v>17111</v>
+        <v>17571</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -4925,7 +4940,7 @@
       </c>
       <c r="C42" s="1">
         <f t="shared" si="1"/>
-        <v>17111</v>
+        <v>17571</v>
       </c>
       <c r="D42" s="1">
         <v>1606</v>
@@ -4940,7 +4955,7 @@
       </c>
       <c r="C43" s="1">
         <f t="shared" si="1"/>
-        <v>18717</v>
+        <v>19177</v>
       </c>
       <c r="D43" s="1">
         <v>980</v>
@@ -4955,7 +4970,7 @@
       </c>
       <c r="C44" s="1">
         <f t="shared" si="1"/>
-        <v>19697</v>
+        <v>20157</v>
       </c>
       <c r="D44" s="1">
         <v>36</v>
@@ -4970,7 +4985,7 @@
       </c>
       <c r="C45" s="1">
         <f t="shared" si="1"/>
-        <v>19733</v>
+        <v>20193</v>
       </c>
       <c r="D45" s="1">
         <v>36</v>
@@ -4985,7 +5000,7 @@
       </c>
       <c r="C46" s="1">
         <f t="shared" si="1"/>
-        <v>19769</v>
+        <v>20229</v>
       </c>
       <c r="D46" s="1">
         <v>15</v>
@@ -5000,7 +5015,7 @@
       </c>
       <c r="C47" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -5015,7 +5030,7 @@
       </c>
       <c r="C48" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -5030,7 +5045,7 @@
       </c>
       <c r="C49" s="1">
         <f t="shared" si="1"/>
-        <v>19784</v>
+        <v>20244</v>
       </c>
       <c r="D49" s="1">
         <v>24</v>
@@ -5045,7 +5060,7 @@
       </c>
       <c r="C50" s="1">
         <f t="shared" si="1"/>
-        <v>19808</v>
+        <v>20268</v>
       </c>
       <c r="D50" s="1">
         <v>616</v>
@@ -5060,7 +5075,7 @@
       </c>
       <c r="C51" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -5075,7 +5090,7 @@
       </c>
       <c r="C52" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -5090,10 +5105,10 @@
       </c>
       <c r="C53" s="1">
         <f t="shared" si="1"/>
-        <v>20424</v>
+        <v>20884</v>
       </c>
       <c r="D53" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -5105,7 +5120,7 @@
       </c>
       <c r="C54" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -5120,7 +5135,7 @@
       </c>
       <c r="C55" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -5135,7 +5150,7 @@
       </c>
       <c r="C56" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -5150,7 +5165,7 @@
       </c>
       <c r="C57" s="1">
         <f t="shared" si="1"/>
-        <v>21264</v>
+        <v>21844</v>
       </c>
       <c r="D57" s="1">
         <v>162</v>
@@ -5637,7 +5652,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7183,7 +7198,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se mantiene</t>
+          <t xml:space="preserve">Se mantiene (En pruebas; sin cambio en esta corrida)</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7254,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se mantiene</t>
+          <t xml:space="preserve">Se mantiene - inicio de pruebas confirmado por prensa (ess-news, 04-09-2026)</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7282,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se mantiene</t>
+          <t xml:space="preserve">Se mantiene - AES proyecta operacion comercial a fines de 2027 (prensa), posterior a la fecha estimada de Min. Energia ago-26</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7422,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJA: entro en operacion (Min. Energia ago-26, Tabla 2)</t>
+          <t xml:space="preserve">BAJA registrada en corrida 2026-09 (ya no integra la lista; el dato vive en las tablas de operacion)</t>
         </is>
       </c>
     </row>
@@ -7604,10 +7619,528 @@
       <c r="B120" t="inlineStr">
         <is>
           <t xml:space="preserve">atribuir cual corresponde a esta fase, por lo que NO se le asigna fabricante (regla 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACTUALIZACION MAIN FUTURE PROJECTS - CORRIDA 2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altas a "A vigilar" (&gt;= ~1000 MWh, con aprobacion ambiental y aun sin construccion), identificadas por investigacion abierta:</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Black BESS (Mack Energy) 350 MW / 1.409 MWh - RCA aprobada abr-2026; inicio de ejecucion previsto dic-2026. Fuente: pv-magazine-latam 09-04-2026; renewablesnow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sidon Solar (Trina Solar Systems Chile) 158 MWdc PV + 1.296 MWh BESS, Biobio/Nuble - RCA aprobada 08-10-2026. Fuente: ess-news 08-10-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin bajas esta corrida: ACERA sep-26 muestra +9 MW / +33 MWh en operacion respecto de ago-26; ningun proyecto &gt;= ~1000 MWh entro en operacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO incorporado por fuente insuficiente: Zelestra Pampino/Monterrico (170 MWac + 1.020 MWh, aprobado 30-09-2026) - unica fuente secundaria no establecida; pendiente de verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota de alcance: las secciones 1 a 6 y la bitacora de esta hoja (market share por fabricante) quedaron fuera de alcance por CLAUDE.md y no se tocaron en esta corrida.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="7" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>BESS Situation in Chile (ACERA, 2026)</t>
+        </is>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="B5" s="1">
+        <f>IF(BESS!E4="","",BESS!E4)</f>
+        <v>1575</v>
+      </c>
+      <c r="C5" s="1">
+        <f>IF(BESS!J4="","",BESS!J4)</f>
+        <v>6384</v>
+      </c>
+      <c r="D5" s="1">
+        <f>IF(BESS!P4="","",BESS!P4)</f>
+        <v>746</v>
+      </c>
+      <c r="E5" s="1">
+        <f>IF(BESS!T4="","",BESS!T4)</f>
+        <v>2688</v>
+      </c>
+      <c r="F5" s="1">
+        <f>IF(BESS!AA4="","",BESS!AA4)</f>
+        <v>7278</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IF(BESS!AE4="","",BESS!AE4)</f>
+        <v>32504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
+      </c>
+      <c r="B6" s="1">
+        <f>IF(BESS!E5="","",BESS!E5)</f>
+        <v>1691</v>
+      </c>
+      <c r="C6" s="1">
+        <f>IF(BESS!J5="","",BESS!J5)</f>
+        <v>6964</v>
+      </c>
+      <c r="D6" s="1">
+        <f>IF(BESS!P5="","",BESS!P5)</f>
+        <v>1486</v>
+      </c>
+      <c r="E6" s="1">
+        <f>IF(BESS!T5="","",BESS!T5)</f>
+        <v>5972</v>
+      </c>
+      <c r="F6" s="1">
+        <f>IF(BESS!AA5="","",BESS!AA5)</f>
+        <v>6596</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IF(BESS!AE5="","",BESS!AE5)</f>
+        <v>29473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
+      </c>
+      <c r="B7" s="1">
+        <f>IF(BESS!E6="","",BESS!E6)</f>
+        <v>1691</v>
+      </c>
+      <c r="C7" s="1">
+        <f>IF(BESS!J6="","",BESS!J6)</f>
+        <v>6964</v>
+      </c>
+      <c r="D7" s="1">
+        <f>IF(BESS!P6="","",BESS!P6)</f>
+        <v>1832</v>
+      </c>
+      <c r="E7" s="1">
+        <f>IF(BESS!T6="","",BESS!T6)</f>
+        <v>7102</v>
+      </c>
+      <c r="F7" s="1">
+        <f>IF(BESS!AA6="","",BESS!AA6)</f>
+        <v>6385</v>
+      </c>
+      <c r="G7" s="1">
+        <f>IF(BESS!AE6="","",BESS!AE6)</f>
+        <v>29018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="B8" s="1">
+        <f>IF(BESS!E7="","",BESS!E7)</f>
+        <v>2063</v>
+      </c>
+      <c r="C8" s="1">
+        <f>IF(BESS!J7="","",BESS!J7)</f>
+        <v>8477</v>
+      </c>
+      <c r="D8" s="1">
+        <f>IF(BESS!P7="","",BESS!P7)</f>
+        <v>2124</v>
+      </c>
+      <c r="E8" s="1">
+        <f>IF(BESS!T7="","",BESS!T7)</f>
+        <v>9730</v>
+      </c>
+      <c r="F8" s="1">
+        <f>IF(BESS!AA7="","",BESS!AA7)</f>
+        <v>5977</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IF(BESS!AE7="","",BESS!AE7)</f>
+        <v>25896</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="B9" s="1">
+        <f>IF(BESS!E8="","",BESS!E8)</f>
+        <v>2063</v>
+      </c>
+      <c r="C9" s="1">
+        <f>IF(BESS!J8="","",BESS!J8)</f>
+        <v>8777</v>
+      </c>
+      <c r="D9" s="1">
+        <f>IF(BESS!P8="","",BESS!P8)</f>
+        <v>2425</v>
+      </c>
+      <c r="E9" s="1">
+        <f>IF(BESS!T8="","",BESS!T8)</f>
+        <v>11275</v>
+      </c>
+      <c r="F9" s="1">
+        <f>IF(BESS!AA8="","",BESS!AA8)</f>
+        <v>5746</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IF(BESS!AE8="","",BESS!AE8)</f>
+        <v>24638</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
+      </c>
+      <c r="B10" s="1">
+        <f>IF(BESS!E9="","",BESS!E9)</f>
+        <v>2318</v>
+      </c>
+      <c r="C10" s="1">
+        <f>IF(BESS!J9="","",BESS!J9)</f>
+        <v>10057</v>
+      </c>
+      <c r="D10" s="1">
+        <f>IF(BESS!P9="","",BESS!P9)</f>
+        <v>2958</v>
+      </c>
+      <c r="E10" s="1">
+        <f>IF(BESS!T9="","",BESS!T9)</f>
+        <v>13593</v>
+      </c>
+      <c r="F10" s="1">
+        <f>IF(BESS!AA9="","",BESS!AA9)</f>
+        <v>4987</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IF(BESS!AE9="","",BESS!AE9)</f>
+        <v>21175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="B11" s="1">
+        <f>IF(BESS!E10="","",BESS!E10)</f>
+        <v>2655</v>
+      </c>
+      <c r="C11" s="1">
+        <f>IF(BESS!J10="","",BESS!J10)</f>
+        <v>11250</v>
+      </c>
+      <c r="D11" s="1">
+        <f>IF(BESS!P10="","",BESS!P10)</f>
+        <v>3151</v>
+      </c>
+      <c r="E11" s="1">
+        <f>IF(BESS!T10="","",BESS!T10)</f>
+        <v>14698</v>
+      </c>
+      <c r="F11" s="1">
+        <f>IF(BESS!AA10="","",BESS!AA10)</f>
+        <v>5040</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IF(BESS!AE10="","",BESS!AE10)</f>
+        <v>21721</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B12" s="1">
+        <f>IF(BESS!E11="","",BESS!E11)</f>
+        <v>3116</v>
+      </c>
+      <c r="C12" s="1">
+        <f>IF(BESS!J11="","",BESS!J11)</f>
+        <v>13522</v>
+      </c>
+      <c r="D12" s="1">
+        <f>IF(BESS!P11="","",BESS!P11)</f>
+        <v>2686</v>
+      </c>
+      <c r="E12" s="1">
+        <f>IF(BESS!T11="","",BESS!T11)</f>
+        <v>12408</v>
+      </c>
+      <c r="F12" s="1">
+        <f>IF(BESS!AA11="","",BESS!AA11)</f>
+        <v>5217</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IF(BESS!AE11="","",BESS!AE11)</f>
+        <v>22330</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="B13" s="1">
+        <f>IF(BESS!E12="","",BESS!E12)</f>
+        <v>3125</v>
+      </c>
+      <c r="C13" s="1">
+        <f>IF(BESS!J12="","",BESS!J12)</f>
+        <v>13555</v>
+      </c>
+      <c r="D13" s="1">
+        <f>IF(BESS!P12="","",BESS!P12)</f>
+        <v>3017</v>
+      </c>
+      <c r="E13" s="1">
+        <f>IF(BESS!T12="","",BESS!T12)</f>
+        <v>13735</v>
+      </c>
+      <c r="F13" s="1">
+        <f>IF(BESS!AA12="","",BESS!AA12)</f>
+        <v>5130</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IF(BESS!AE12="","",BESS!AE12)</f>
+        <v>22123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="str">
+        <f>IF(BESS!E13="","",BESS!E13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="1" t="str">
+        <f>IF(BESS!J13="","",BESS!J13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="1" t="str">
+        <f>IF(BESS!P13="","",BESS!P13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f>IF(BESS!T13="","",BESS!T13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="1" t="str">
+        <f>IF(BESS!AA13="","",BESS!AA13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f>IF(BESS!AE13="","",BESS!AE13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="str">
+        <f>IF(BESS!E14="","",BESS!E14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f>IF(BESS!J14="","",BESS!J14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="1" t="str">
+        <f>IF(BESS!P14="","",BESS!P14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f>IF(BESS!T14="","",BESS!T14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="1" t="str">
+        <f>IF(BESS!AA14="","",BESS!AA14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f>IF(BESS!AE14="","",BESS!AE14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="str">
+        <f>IF(BESS!E15="","",BESS!E15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f>IF(BESS!J15="","",BESS!J15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="1" t="str">
+        <f>IF(BESS!P15="","",BESS!P15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f>IF(BESS!T15="","",BESS!T15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="1" t="str">
+        <f>IF(BESS!AA15="","",BESS!AA15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f>IF(BESS!AE15="","",BESS!AE15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolida unicamente las columnas de fuente ACERA de las seis tablas de la hoja BESS (E/J/P/T/AA/AE). Son formulas: se actualiza sola cada corrida. Celda vacia = ACERA aun no publico ese dato (no se estima).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+</worksheet>
 </file>